--- a/output/upload/S00027_1726_e정기보험_무배당.xlsx
+++ b/output/upload/S00027_1726_e정기보험_무배당.xlsx
@@ -2611,17 +2611,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -2702,17 +2694,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -2793,17 +2777,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -2884,17 +2860,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -2975,17 +2943,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -3066,17 +3026,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
@@ -3157,17 +3109,9 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
@@ -3248,17 +3192,9 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="inlineStr">
@@ -3338,16 +3274,8 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3391,16 +3319,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3444,16 +3364,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3497,16 +3409,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3550,16 +3454,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3603,16 +3499,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3656,16 +3544,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_1726_e정기보험_무배당.xlsx
+++ b/output/upload/S00027_1726_e정기보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW21"/>
+  <dimension ref="A1:AW27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="L8" s="6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="N9" s="6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="L10" s="6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="L12" s="6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="L14" s="6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -3423,12 +3423,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -3558,31 +3558,301 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>90</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>90</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>X100</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>100</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>X100</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="L23" t="n">
         <v>100</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>20</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="N21" t="n">
+      <c r="L24" t="n">
         <v>100</v>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>100</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>10</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>10</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>10</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>20</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>10</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>10</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_1726_e정기보험_무배당.xlsx
+++ b/output/upload/S00027_1726_e정기보험_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2694,11 +2714,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2777,11 +2817,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2860,11 +2920,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2943,11 +3023,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3026,11 +3126,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3109,11 +3229,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3192,11 +3332,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3274,8 +3434,31 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3319,8 +3502,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3364,8 +3570,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3409,8 +3638,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3454,8 +3706,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3499,8 +3774,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3544,8 +3842,31 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3589,8 +3910,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3634,8 +3978,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3679,8 +4046,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3724,8 +4114,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3769,8 +4182,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3814,8 +4250,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_1726_e정기보험_무배당.xlsx
+++ b/output/upload/S00027_1726_e정기보험_무배당.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">

--- a/output/upload/S00027_1726_e정기보험_무배당.xlsx
+++ b/output/upload/S00027_1726_e정기보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW27"/>
+  <dimension ref="A1:AW86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -4252,22 +4252,22 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>1726039</t>
+          <t>1726040</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1726039</t>
+          <t>1726040</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4287,21 +4287,21 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>N10</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -4312,6 +4312,4018 @@
         <v>10</v>
       </c>
       <c r="O27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>60</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>20</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>60</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>60</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>65</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>65</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>20</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>65</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>65</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>70</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>10</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>70</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>20</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>70</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>70</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>80</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>10</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>80</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>20</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>80</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>80</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>90</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>10</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>90</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>20</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>90</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>90</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>100</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>10</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>100</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>20</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>100</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>100</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>10</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>10</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>20</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>60</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>10</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>60</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>20</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>60</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>60</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>65</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>10</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>65</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>20</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>65</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>65</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>70</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>10</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>70</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>20</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>70</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>70</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>80</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>10</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>80</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>20</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>80</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>80</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>90</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>10</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>90</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>20</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>90</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>90</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>100</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>10</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>100</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>20</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>100</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>100</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>10</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>10</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>10</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>20</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>60</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>10</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>60</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>20</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>60</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>60</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>65</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>10</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>65</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>20</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>65</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>65</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>70</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>10</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>70</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>20</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>70</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>70</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>80</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>10</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>80</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>20</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>80</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>80</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>90</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>10</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>90</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>20</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>90</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>90</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>100</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>10</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>100</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>20</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>100</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>100</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>10</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>10</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>10</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>20</v>
+      </c>
+      <c r="O86" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_1726_e정기보험_무배당.xlsx
+++ b/output/upload/S00027_1726_e정기보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW86"/>
+  <dimension ref="A1:AW74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -2658,11 +2658,11 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="N8" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -2872,11 +2872,11 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N9" s="6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
@@ -2957,12 +2957,12 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -2971,15 +2971,15 @@
         </is>
       </c>
       <c r="L10" s="6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -3181,11 +3181,11 @@
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -3280,15 +3280,15 @@
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3489,11 +3489,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3553,15 +3553,15 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3693,11 +3693,11 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3743,12 +3743,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3757,15 +3757,15 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3897,11 +3897,11 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3947,12 +3947,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3961,15 +3961,15 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -4101,11 +4101,11 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -4151,29 +4151,29 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -4184,22 +4184,22 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>1726039</t>
+          <t>1726040</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1726039</t>
+          <t>1726040</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -5476,22 +5476,22 @@
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>1726040</t>
+          <t>1726041</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1726040</t>
+          <t>1726041</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5511,21 +5511,21 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t>N10</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -5544,22 +5544,22 @@
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>1726040</t>
+          <t>1726041</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1726040</t>
+          <t>1726041</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5589,11 +5589,11 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -5647,12 +5647,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5661,15 +5661,15 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -5715,12 +5715,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5729,7 +5729,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -5783,12 +5783,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5797,15 +5797,15 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5865,15 +5865,15 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -5919,12 +5919,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -5987,12 +5987,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6001,15 +6001,15 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -6069,15 +6069,15 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -6123,12 +6123,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -6205,15 +6205,15 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -6259,12 +6259,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -6273,15 +6273,15 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -6327,12 +6327,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -6395,12 +6395,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -6409,15 +6409,15 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6477,15 +6477,15 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -6496,22 +6496,22 @@
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6531,12 +6531,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -6564,22 +6564,22 @@
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6613,15 +6613,15 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -6632,22 +6632,22 @@
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6667,12 +6667,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6681,15 +6681,15 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -6700,22 +6700,22 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -6768,22 +6768,22 @@
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6817,15 +6817,15 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -6836,22 +6836,22 @@
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6871,29 +6871,29 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -6904,22 +6904,22 @@
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1726041</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6939,29 +6939,29 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>N10</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>80</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L66" t="n">
+      <c r="N66" t="n">
         <v>10</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>20</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -7021,7 +7021,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -7075,12 +7075,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -7089,15 +7089,15 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -7143,12 +7143,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -7157,15 +7157,15 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -7211,12 +7211,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -7279,12 +7279,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7293,15 +7293,15 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -7347,12 +7347,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X65</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7361,15 +7361,15 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -7483,12 +7483,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7497,833 +7497,17 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O74" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>X70</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>X70</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L75" t="n">
-        <v>70</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N75" t="n">
-        <v>70</v>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>X80</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L76" t="n">
-        <v>80</v>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N76" t="n">
-        <v>10</v>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>X80</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L77" t="n">
-        <v>80</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N77" t="n">
-        <v>20</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>X80</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>X80</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L78" t="n">
-        <v>80</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N78" t="n">
-        <v>80</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L79" t="n">
-        <v>90</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N79" t="n">
-        <v>10</v>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L80" t="n">
-        <v>90</v>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N80" t="n">
-        <v>20</v>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L81" t="n">
-        <v>90</v>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N81" t="n">
-        <v>90</v>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L82" t="n">
-        <v>100</v>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N82" t="n">
-        <v>10</v>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L83" t="n">
-        <v>100</v>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N83" t="n">
-        <v>20</v>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L84" t="n">
-        <v>100</v>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N84" t="n">
-        <v>100</v>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L85" t="n">
-        <v>10</v>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N85" t="n">
-        <v>10</v>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L86" t="n">
-        <v>10</v>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N86" t="n">
-        <v>20</v>
-      </c>
-      <c r="O86" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>
